--- a/outputs/excel/dataset_avec_preds.xlsx
+++ b/outputs/excel/dataset_avec_preds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,15 +501,20 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>ns_score_calc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ns_label_calc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>electre_cat</t>
         </is>
@@ -518,63 +523,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Croustillant Chocolat – Bjorg – 500 g</t>
+          <t>4 Petits Pains sans Sel – Picard – 160 g</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1811.672</v>
+        <v>1020.896</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>0.02</v>
       </c>
       <c r="F2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>-5</v>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>A'</t>
         </is>
@@ -583,741 +589,752 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premium Granola Super Nussig – Crownfield – 500 g</t>
+          <t>Apple and cinnamon flakes – Marks &amp; Spencer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1958.112</v>
+        <v>1581.552</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>19.7</v>
+        <v>15.4</v>
       </c>
       <c r="E3" t="n">
+        <v>372</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>29</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>57</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHEERIOS BIO Céréale 375g – Nestlé </t>
+          <t>Auchan cereales coeur chocolat au lait – Auchan</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1623.392</v>
+        <v>1778.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="F4" t="n">
-        <v>9.1</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>9.9</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>58</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Color Loops – Turtle Cereals – 40g</t>
+          <t>Auchan cereales coeur lait 400g – Auchan, Jumblies</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1510.424</v>
+        <v>1832.592</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="D5" t="n">
-        <v>19.8</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Céréales Marshmallow Crunchies – Turtle – 300 g</t>
+          <t>Automne - Hiver - 3 chocolats – Cruesli, PepsiCo, Quaker</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1652.68</v>
+        <v>1966.48</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="F6" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.844</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>11</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>D'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LION BIO Céréales 400g – Nestlé – 400 g</t>
+          <t>Belvita Petit Déjeuner Chocolat – LU, Mondelez</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1719.624</v>
+        <v>1840.96</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="F7" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="G7" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>7</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>11</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pillows Peanut butter – Turtle – 300 g</t>
+          <t>BelVita Petit Déjeuner Duo Fourré goût Chocolat Noisette – LU</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1815.856</v>
+        <v>1882.8</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="F8" t="n">
-        <v>11.6</v>
+        <v>7.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>12</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>D'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multigrain Flakes Chocolate – Turtle – 300 g</t>
+          <t>Biscuits Matin Miel et Pépites de Chocolat – Casino</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1623.392</v>
+        <v>2058.528</v>
       </c>
       <c r="C9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>14</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHOCAPIC BIO Céréales 375g – Nestlé – 375 g</t>
+          <t>Biscuits Petit déjeuner Céréales Pépites de Chocolat et Noisettes – Carrefour BIO, Carrefour</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1635.944</v>
+        <v>2062.712</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="D10" t="n">
-        <v>22.5</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="F10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.9</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>74</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>45</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Corn flakes – Carrefour BIO – 500 g</t>
+          <t>Biscuits P'tit Déj Abricots, Amandes et Pépites de chocolat – Leader Price</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1606.656</v>
+        <v>1983.216</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>11</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NESTLE NESQUIK BIO Céréales 375g</t>
+          <t>Boules céréales miel – Marque Repère, Brin de Jour</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1564.816</v>
+        <v>1635.944</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>22.3</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>9.1</v>
+        <v>5.8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>46</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Céréales All Bran Kellogg's Fibre Plus – 500 g</t>
+          <t>Boules Chocolat – Swing</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1397.456</v>
+        <v>1585.736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>11</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Granola Honing -Miel – Crownfield – 500 g</t>
+          <t>Boules de céréales au chocolat – Eco+ – 750 g</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1765.648</v>
+        <v>1556.448</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.1</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>0.43</v>
       </c>
       <c r="F14" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1328,293 +1345,298 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>6</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>-5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jordans crunchy granola – 850g</t>
+          <t>Boules maïs miel – Cora</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1736.36</v>
+        <v>1631.76</v>
       </c>
       <c r="C15" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>380</v>
       </c>
       <c r="F15" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>6</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>13</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>D'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Krounchy nature – Grillon d'Or – 1 kg</t>
+          <t>Boules soufflées au chocolat – Cénos</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1840.96</v>
+        <v>1619.208</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="F16" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>31</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>50</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>crunch – Nestlé – 500g</t>
+          <t>Cacao &amp; Wheat Pillows – Golden bridge</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1686.152</v>
+        <v>2016.688</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F17" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="G17" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>6</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>13</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pétal'choco 375 g - P'tits Prods – Chabrior</t>
+          <t>Cannellones complètes – Naturaline – 250 g</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1602.472</v>
+        <v>1564.816</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>8.800000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="G18" t="n">
-        <v>9.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>-5</v>
       </c>
       <c r="Q18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>A'</t>
         </is>
@@ -1623,354 +1645,359 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Crunchy muesli – Boni</t>
+          <t>Carré craquant à la framboise – Marque Repère, Brin de Jour</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1845.144</v>
+        <v>1602.472</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="F19" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="G19" t="n">
-        <v>9.1</v>
+        <v>3.9</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>7</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>11</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coco Pops Chocos – Kellogg's</t>
+          <t>Carrés miel – Cora</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1589.92</v>
+        <v>1594.104</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>31.5</v>
       </c>
       <c r="E20" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>39</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>10</v>
       </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>25</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Crunchy muesli au chocolat – Bony – 750 g</t>
+          <t>Céréales</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1874.432</v>
+        <v>1333.8592</v>
       </c>
       <c r="C21" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>0.88</v>
       </c>
       <c r="F21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>-1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peanut butter puffs imp – Reese's – 326g</t>
+          <t>Cereales – Nestlé</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1715.44</v>
+        <v>1589.92</v>
       </c>
       <c r="C22" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="D22" t="n">
-        <v>30.8</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>7.69</v>
+        <v>4.7</v>
       </c>
       <c r="G22" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.649999999999999</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>13</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>19</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
       <c r="M22" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>13</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kellogg's Frosted Flakes Cereal</t>
+          <t>Céréales All Bran Kellogg's Fibre Plus – 500 g</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1585.736</v>
+        <v>1397.456</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D23" t="n">
-        <v>34.48</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>597</v>
+        <v>380</v>
       </c>
       <c r="F23" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4</v>
+        <v>27</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>14</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>6</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Riz Soufflé Enrobé de Chocolat – U – 375 g e</t>
+          <t>Céréales Extra Kellogg's Pépites Chocolat au lait – 500 g</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1644.312</v>
+        <v>2025.056</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>33.6</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>452</v>
+        <v>0.73</v>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1978,64 +2005,65 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>15</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fourrées tout choco – Cora – 500 g</t>
+          <t>Céréales Extra Pepites Kellogg's Chocolat au lait – 800 g</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1794.936</v>
+        <v>2025.056</v>
       </c>
       <c r="C25" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2043,10 +2071,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2054,89 +2082,5579 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>11</v>
-      </c>
-      <c r="P25" t="inlineStr">
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>A'</t>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Céréales Marshmallow Crunchies – Turtle – 300 g</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1652.68</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>160</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>45</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Céréales Muesli floconneux chocolat noir et graines de courge 375g – U – 375 g</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1623.392</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>82</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Céréales Trésor Kellogg's Chocolat Noisettes - 1kg – 1000 g</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B28" t="n">
         <v>1907.904</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C28" t="n">
         <v>3.5</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D28" t="n">
         <v>26</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>452</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>7</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>3.5</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H28" t="n">
         <v>2.583</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>19</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>8</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>20</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>15</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHEERIOS BIO Céréale 375g – Nestlé </t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1623.392</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>268</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>58</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chickpea - pasta organic – Kazidomi – 250 g</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1405.824</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>95</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHOCAPIC BIO Céréales 375g – Nestlé – 375 g</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1635.944</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>45</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Choco Smile – Country Farm</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1577.368</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>160</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>13</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>31</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Coco Pops Chocos – Kellogg's</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1589.92</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>22</v>
+      </c>
+      <c r="E33" t="n">
+        <v>320</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>25</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Color Loops – Turtle Cereals – 40g</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1510.424</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>280</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>45</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Corn flakes – Carrefour BIO – 500 g</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1606.656</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>180</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>45</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Corn Flakes sucrées – Eco + – 750 g e (2 * 375 g)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1619.208</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>13</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>45</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Couscous au chanvre – Priméal – 500 g</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1627.576</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>86</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Crème sésame noir – Jean Hervé – 350 g</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2619.184</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>51</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Croc'Choco Blanc – Lucien Georgelin – 375g</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1820.04</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D39" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>46</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CR'OCKS au chocolat au lait – Carrefour, Xtrem</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1778.2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>240</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>14</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>29</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CROCKS Goût CHOCO-NOISETTE – Carrefour, Xtrem</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1907.904</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26</v>
+      </c>
+      <c r="E41" t="n">
+        <v>248</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>13</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>30</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Croustillant Chocolat – Bjorg – 500 g</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1811.672</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" t="n">
+        <v>112</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>crunch – Nestlé – 500g</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1686.152</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>15</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Crunchy muesli – Boni</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1845.144</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>19</v>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>18</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>62</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Crunchy muesli au chocolat – Bony – 750 g</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1874.432</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>19</v>
+      </c>
+      <c r="E45" t="n">
+        <v>32</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>77</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Epicerie / Epicerie Sucrée / Galettes Riz Et Céréales – Primeal – 100 g</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1556.448</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F46" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>87</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Farine de millet brun – BIOSAGESSE – 500 g</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1577.368</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>94</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Farine d'épeautre T80 – MelBio – 1 kg</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1456.032</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>94</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fourrées tout choco – Cora – 500 g</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1794.936</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>44</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>19</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>25</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Galettes à base d'épeautre 130g – U – 130 g</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1514.608</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>11</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>64</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Grains d epautre complet bio – Bio sonne – 750 g</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1443.48</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>17</v>
+      </c>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>95</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Granola amande &amp; miel – Aline &amp; Olivier – 310 g</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1870.248</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F52" t="n">
+        <v>11</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>82</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Granola Honing -Miel – Crownfield – 500 g</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1765.648</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>57</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Grissino gusto classico – Vialatina – 200 g e</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1719.624</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>94</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jordans crunchy granola – 850g</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1736.36</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>22</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H55" t="n">
+        <v>18</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>57</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Kallo Natures Rice Cake imp – kallø – 130 g</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1648.496</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>64</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kelloggs extra aux 3 fruits rouges – Kellogg's – 500g</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2071.08</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D57" t="n">
+        <v>22</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>21</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>45</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Kellogg's Frosted Flakes Cereal</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1585.736</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="E58" t="n">
+        <v>597</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>19</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>25</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Krounchy nature – Grillon d'Or – 1 kg</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1840.96</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>20</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LION BIO Céréales 400g – Nestlé – 400 g</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1719.624</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>164</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>10</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>45</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mélange de 5 céréales – Monoprix Bio – 500 g</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>13</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>99</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>mélange pour pain aux graines – Adams Brot – 250 g</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1046</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>42</v>
+      </c>
+      <c r="G62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>97</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mix' Galettes petit épeautre &amp; soja – Priméal – 250 g</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1640.128</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F63" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G63" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>88</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>muesli ensoleillé fruit d'été – bjorg – 375 g</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1556.448</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>82</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Multigrain Flakes Chocolate – Turtle – 300 g</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1623.392</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>180</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>6</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>45</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NESTLE NESQUIK BIO Céréales 375g</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1564.816</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>180</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>46</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NESTLE NESQUIK BIO Céréales 375g</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1564.816</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>180</v>
+      </c>
+      <c r="F67" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>46</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pain aux 5 graines tournesol sesam avoine lin et millet – Mercadona – 500g</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1146.416</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F68" t="n">
+        <v>11</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>70</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pain complet de seigle aux graines de tournesol – Céréal BIO – 500 g</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>895.3760000000001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>11</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>97</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pain complet de seigle aux graines de tournesol – Céréal BIO – 500 g</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>895.3760000000001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G70" t="n">
+        <v>11</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>97</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pain de mie complet Grandes Tranches – Auchan – 0.825 kg</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1083.656</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>74</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pain de mie grandes tranches complet – Marque Repère – 550 g</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1066.92</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F72" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G72" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>70</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>pain de mie grandes tranches spécial sandwich complet – Maître Jean Pierre – 750 g</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1079.472</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G73" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>74</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Pâte feuilletée pur beurre – Marque Repère – 230 g</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1543.896</v>
+      </c>
+      <c r="C74" t="n">
+        <v>14</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>19</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>69</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Peanut butter puffs imp – Reese's – 326g</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1715.44</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>564</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>8.649999999999999</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>25</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Peanut butter puffs imp – Reese's – 326g</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1715.44</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D76" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>564</v>
+      </c>
+      <c r="F76" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>19</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>25</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>D'</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Penne Rigate au blé complet bio – Casino – 500 g</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1447.664</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F77" t="n">
+        <v>13</v>
+      </c>
+      <c r="G77" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>82</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Penne Rigate au blé complet bio – Casino – 500 g</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1447.664</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F78" t="n">
+        <v>13</v>
+      </c>
+      <c r="G78" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>82</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Pétal'choco 375 g - P'tits Prods – Chabrior</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1602.472</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>23</v>
+      </c>
+      <c r="E79" t="n">
+        <v>44</v>
+      </c>
+      <c r="F79" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G79" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>30</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Pétal'choco 375 g - P'tits Prods – Chabrior</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1602.472</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>23</v>
+      </c>
+      <c r="E80" t="n">
+        <v>44</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>30</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Pillows Peanut butter – Turtle – 300 g</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1815.856</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E81" t="n">
+        <v>48</v>
+      </c>
+      <c r="F81" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>35</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>45</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pillows Peanut butter – Turtle – 300 g</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1815.856</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E82" t="n">
+        <v>48</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>35</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>45</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Pizza pâte complète</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>970.688</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>91</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Pizza pâte complète</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>970.688</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>91</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/8414897100583/pain-aux-5-graines-tournesol-sesam-avoine-lin-et-millet-mercadona</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Polenta aux cepes – Moulin des Moines – 250 g</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1535.528</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G85" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>86</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3175681085688/pain-complet-de-seigle-aux-graines-de-tournesol-cereal-bio</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Polenta aux cepes – Moulin des Moines – 250 g</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1535.528</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>86</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3596710497720/pain-de-mie-complet-grandes-tranches-auchan</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Polenta de féverole complète – Graine de choc – 1 kg</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1334.696</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F87" t="n">
+        <v>30</v>
+      </c>
+      <c r="G87" t="n">
+        <v>15</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>97</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3564700596968/pain-de-mie-grandes-tranches-complet-marque-repere</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Polenta de féverole complète – Graine de choc – 1 kg</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1334.696</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F88" t="n">
+        <v>30</v>
+      </c>
+      <c r="G88" t="n">
+        <v>15</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>97</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/4056489007180/pain-de-mie-grandes-tranches-special-sandwich-complet-maitre-jean-pierre</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Porridge figue framboise – Bjorg – 375 g</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1518.792</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>13</v>
+      </c>
+      <c r="G89" t="n">
+        <v>10</v>
+      </c>
+      <c r="H89" t="n">
+        <v>9</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>87</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3564700098905/pate-feuilletee-pur-beurre-marque-repere</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Porridge figue framboise – Bjorg – 375 g</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1518.792</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F90" t="n">
+        <v>13</v>
+      </c>
+      <c r="G90" t="n">
+        <v>10</v>
+      </c>
+      <c r="H90" t="n">
+        <v>9</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>87</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Premium Granola Super Nussig – Crownfield – 500 g</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1958.112</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E91" t="n">
+        <v>12</v>
+      </c>
+      <c r="F91" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>16</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>9</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>57</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Penne Rigate au blé complet bio – Casino – 500 g</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Premium Granola Super Nussig – Crownfield – 500 g</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1958.112</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E92" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>16</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>9</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>57</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Quaker Muesli Croustillant Myrtilles &amp; baies de goji – 500 g</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1681.968</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>14</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="F93" t="n">
+        <v>11</v>
+      </c>
+      <c r="G93" t="n">
+        <v>14</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>67</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ramen soja caramel – Tanoshi – 360 g</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>681.9920000000001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H94" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>67</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/5425003741067/pate-a-pizza</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ravioli – Belle France – 400 g e</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>410.032</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>15</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>75</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Polenta aux cepes – Moulin des Moines – 250 g</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ravioli – Belle France – 400 g e</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>410.032</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>15</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>75</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Polenta de féverole complète – Graine de choc – 1 kg</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Riz Soufflé Enrobé de Chocolat – U – 375 g e</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1644.312</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>452</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>19</v>
+      </c>
+      <c r="K97" t="n">
+        <v>3</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>29</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3229820792965/porridge-figue-framboise-bjorg</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Riz Soufflé Enrobé de Chocolat – U – 375 g e</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1644.312</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D98" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E98" t="n">
+        <v>452</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>19</v>
+      </c>
+      <c r="K98" t="n">
+        <v>3</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>29</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Semoule De Blé Fine Complète Bio – La Vie Claire – 500 g</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1454.3584</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G99" t="n">
+        <v>8</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>86</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3168930009801/quaker-muesli-croustillant-myrtilles-baies-de-goji</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Semoule De Blé Fine Complète Bio – La Vie Claire – 500 g</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1454.3584</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>8</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>86</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3229820181363/ramen-soja-caramel-tanoshi</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tartines Bio craquantes aux pois chiches sans gluten – Ekibio – 150 g, 2 sachets</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1581.552</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F101" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>91</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Ravioli – Belle France – 400 g e</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Tartines Bio craquantes aux pois chiches sans gluten – Ekibio – 150 g, 2 sachets</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1581.552</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="F102" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G102" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>91</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Thyme – Kellogg's – 1 kg</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1665.232</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D103" t="n">
+        <v>35</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>23</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>25</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>https://mescoursesenligne.lavieclaire.com/product/semoule-de-ble-fine-complete-bio/</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Trésor – Kellogg's – 410 g</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1811.672</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>26</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>11</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>20</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>45</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/3380380080050/tartines-bio-craquantes-aux-pois-chiches-sans-gluten-ekibio</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Trésor – Kellogg's – 410 g</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1811.672</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>26</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>11</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>20</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>45</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/5050083459825/thyme-kellogg-s</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wraps au blé nature – Mission – 370 g</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1313.776</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>73</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/5053827199568/tresor-kellogg-s#panel_environmental_score</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Wraps intégral Blé complet – Mission</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1213.36</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G107" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>9</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>93</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/8710637105352/wraps-au-ble-nature-mission</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Wraps intégral Blé complet – Mission</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1213.36</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G108" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>9</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>93</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>https://fr.openfoodfacts.org/produit/8710637105628/wraps-integral-ble-complet-mission</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>B'</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/dataset_avec_preds.xlsx
+++ b/outputs/excel/dataset_avec_preds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,55 +517,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>wasa</t>
+          <t>Oatly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aliments d'origine végétale,Snacks,Céréales et pommes de terre,Pains,Pains croustillants,Petit-déjeuners</t>
+          <t>Beverages and beverages preparations, Plant-based foods and beverages, Beverages, Plant-based foods, Cereals and potatoes, Dairy substitutes, Cereals and their products, Milk substitutes, Plant-based beverages, Plant-based milk alternatives, Cereal-based drinks, Oat-based drinks</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1415</v>
+        <v>255</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tartine croustillante Authentique</t>
+          <t>Oat Drink Barista Edition</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>0.039</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -574,61 +574,61 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wasa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Aliments d'origine végétale,Snacks,Céréales et pommes de terre,Pains,Pains croustillants,Petit-déjeuners</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tartine croustillante Authentique</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>la Boulangère</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Pains de mie</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1246</v>
-      </c>
-      <c r="E3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Pain de mie grandes tranches Seigle &amp; Graines 500g</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.2</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -647,51 +647,51 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jacquet</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Sliced breads,Wholemeal breads,Wholemeal sliced breads</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1026</v>
+        <v>1500</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14 Maxi Tranches complet sans sucres ajoutés</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3</v>
+        <v>0.526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.48</v>
+        <v>0.103</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -710,22 +710,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Krisprolls</t>
+          <t>Kallo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Toasts,Toasted bread rolls</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Puffed cereal cakes,Puffed rice cakes,Puffed wholegrain rice cakes</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1687</v>
+        <v>1585</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="F5" t="n">
-        <v>8.300000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,24 +737,24 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Krisprolls complets sans sucres ajoutés</t>
+          <t>Organic Lightly Salted Wholegrain Low Fat Rice Cakes</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>0.22</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -769,26 +769,26 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>la Boulangère</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Crispbreads,Crispbreads(wholemeal), Snacks, Snacks salés, Amuse-gueules, Chips et frites, Chips</t>
+          <t>Pains de mie</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1397</v>
+        <v>1246</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FIBRES</t>
+          <t>Pain de mie grandes tranches Seigle &amp; Graines 500g</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -810,16 +810,14 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.48</v>
+        <v>0.384</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -834,55 +832,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quaker</t>
+          <t>Krisprolls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Mueslis,Cereals with nuts,Crunchy cereal clusters,Cereal clusters with nuts</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Toasts,Toasted bread rolls</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1913</v>
+        <v>1687</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cruesly mélange de noix</t>
+          <t>Krisprolls complets sans sucres ajoutés</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -891,7 +889,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -901,51 +899,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La Boulangère,La Boulangère Bio</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Sliced breads,Packaged breads,Wholemeal breads,Wholemeal sliced breads,fr:écologie</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Crispbreads,Crispbreads(wholemeal), Snacks, Snacks salés, Amuse-gueules, Chips et frites, Chips</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1131</v>
+        <v>1397</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pain De Mie Bio</t>
+          <t>FIBRES</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -964,51 +964,51 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Jacquet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Flakes,Cereal flakes,Rolled flakes,Rolled oats</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Sliced breads,Wholemeal breads,Wholemeal sliced breads</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1524</v>
+        <v>1026</v>
       </c>
       <c r="E9" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Flocons d'avoine</t>
+          <t>14 Maxi Tranches complet sans sucres ajoutés</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008</v>
+        <v>0.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1017,187 +1017,187 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ekibio,Le pain des Fleurs</t>
+          <t>Quaker</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Snacks,Cereals and potatoes,Cereals and their products,Extruded crispbreads</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Mueslis,Cereals with nuts,Crunchy cereal clusters,Cereal clusters with nuts</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1631</v>
+        <v>1913</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tartines craquantes au sarrasin imp</t>
+          <t>cruesly mélange de noix</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13.4</v>
+        <v>8.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Ekibio,Le pain des Fleurs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals rich in fibre,Crunchy cereal clusters,Cereal clusters with chocolate</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Snacks,Cereals and potatoes,Cereals and their products,Extruded crispbreads</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1812</v>
+        <v>1631</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Croustillant Chocolat</t>
+          <t>Tartines craquantes au sarrasin imp</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9.800000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.112</v>
+        <v>0.272</v>
       </c>
       <c r="M11" t="n">
-        <v>14</v>
+        <v>2.6</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lidl,Maître Jean Pierre</t>
+          <t>Brownfield, CROWNFIELD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains de mie,Pains complets,Pains de mie complet</t>
+          <t>Alimente și băuturi pe bază de plante,Alimente pe bază de plante,en:Breakfasts,Cereale și cartofi,en:Cereals and their products,en:Breakfast cereals,en:Flakes,en:Cereal flakes,en:Extruded flakes,en:Rolled flakes,en:Rolled oats,Cereale</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1089</v>
+        <v>1556</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>pain de mie grandes tranches spécial sandwich complet</t>
+          <t>Haferflocken</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8.300000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>0.012</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1216,22 +1216,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits,Müesli</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Special Muesli 30% fruits &amp; noix</t>
+          <t>Family Pack</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.012</v>
+        <v>0.11</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1279,53 +1279,51 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Harrys</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Snacks, Snacks sucrés, Viennoiseries, Brioches, Brioches tressées, Brioches pur beurre, Brioches natures, Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Pains, en:Packaged breads</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Flakes,Cereal flakes,Rolled flakes,Rolled oats</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1496</v>
+        <v>1524</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>7.1</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Harrys brioche tressee nature au sucre perle sans additifs 500g</t>
+          <t>Flocons d'avoine</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0.32</v>
+        <v>0.008</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1334,72 +1332,70 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barilla,Wasa</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Crispbreads,fr:Pains croustillants complets, Snacks, Snacks salés, Amuse-gueules, Chips et frites, Chips</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals rich in fibre,Crunchy cereal clusters,Cereal clusters with chocolate</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1423</v>
+        <v>1812</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>wasa</t>
+          <t>Croustillant Chocolat</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>0.112</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
@@ -1409,60 +1405,60 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>La Boulangère,La Boulangère Bio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Sliced breads,Packaged breads,Wholemeal breads,Wholemeal sliced breads,fr:écologie</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1485</v>
+        <v>1131</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Muesli Raisin, Figue, Abricot</t>
+          <t>Pain De Mie Bio</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.012</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>6.3</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1472,51 +1468,51 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jardin Bio</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Snacks,Cereals and potatoes,Cereals and their products,Extruded crispbreads</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Breakfast cereals rich in fibre,fr:Weetabix</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1603</v>
+        <v>1516</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tartines craquantes quinoa - pois chiche</t>
+          <t>Weetabix produit à base de blé complet 100%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.104</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1535,53 +1531,51 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Harry's</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains de mie,Pains de mie sans croûte,Pains complets,Pains de mie complet</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1053</v>
+        <v>1485</v>
       </c>
       <c r="E18" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100% mie complet 500g</t>
+          <t>Muesli Raisin, Figue, Abricot</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="L18" t="n">
-        <v>0.44</v>
+        <v>0.012</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1590,7 +1584,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1600,51 +1594,51 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits,Müesli</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1498</v>
+        <v>1523</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="F19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Special Muesli 30% fruits &amp; noix</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>10</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Muesli SuperFruits Raisins, cassis,cranberry, myrtille</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>11</v>
-      </c>
       <c r="K19" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="M19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1653,7 +1647,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -1663,51 +1657,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>La Boulangère</t>
+          <t>Lidl,Maître Jean Pierre</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Sliced breads,Multigrain sliced breads, Céréales et dérivés, en:Packaged breads</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains de mie,Pains complets,Pains de mie complet</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1306</v>
+        <v>1089</v>
       </c>
       <c r="E20" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pain de mie Bio grandes tranches céréales &amp; graines 500g</t>
+          <t>pain de mie grandes tranches spécial sandwich complet</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
         <v>0.4</v>
       </c>
       <c r="M20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1722,55 +1716,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Barilla,Wasa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Crispbreads,fr:Pains croustillants complets, Snacks, Snacks salés, Amuse-gueules, Chips et frites, Chips</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1423</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>wasa</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LU Pelletier</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Rusks,Toasts</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1636</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Pain grillé au blé complet</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>12</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1779,7 +1775,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1789,53 +1785,53 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Harry's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Flakes, Cereal flakes, Extruded cereals, Extruded flakes, Corn flakes</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains de mie,Pains de mie sans croûte,Pains complets,Pains de mie complet</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1604</v>
+        <v>1053</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Corn Flakes</t>
+          <t>100% mie complet 500g</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L22" t="n">
         <v>0.44</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1844,7 +1840,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1854,60 +1850,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Jardin Bio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Breakfast cereals rich in fibre,Cereals with nuts,Crunchy cereal clusters,Cereal clusters with nuts</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Snacks,Cereals and potatoes,Cereals and their products,Extruded crispbreads</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1949</v>
+        <v>1603</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Country Crisp 4 noix</t>
+          <t>Tartines craquantes quinoa - pois chiche</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0.012</v>
+        <v>0.2</v>
       </c>
       <c r="M23" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1917,60 +1913,62 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quaker</t>
+          <t>Harrys</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
+          <t>Snacks, Snacks sucrés, Viennoiseries, Brioches, Brioches tressées, Brioches pur beurre, Brioches natures, Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Pains, en:Packaged breads</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1570</v>
+        <v>1496</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Flocons d'avoine complète</t>
+          <t>Harrys brioche tressee nature au sucre perle sans additifs 500g</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004</v>
+        <v>0.32</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -1980,114 +1978,114 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maïzena, Unilever</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Aides culinaires, Amidons, Amidons de céréales, Amidon de maïs</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1487</v>
+        <v>1498</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Maizena Fleur de Maïs Sans Gluten 400g</t>
+          <t>Muesli SuperFruits Raisins, cassis,cranberry, myrtille</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5</v>
+        <v>13</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Weetabix</t>
+          <t>Oatly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Breakfast cereals rich in fibre,fr:Weetabix</t>
+          <t>Getränke und Getränkezubereitungen, Pflanzliche Lebensmittel und Getränke, Getränke, Pflanzliche Lebensmittel, Getreide und Kartoffeln, en:Dairy substitutes, Getreideprodukte, Milchersatz, Pflanzliche Getränke, Pflanzenmilch, Getreidemilch, Hafermilch</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1516</v>
+        <v>257</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Weetabix produit à base de blé complet 100%</t>
+          <t>Haferdrink Barista</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.53</v>
+        <v>0.3</v>
       </c>
       <c r="L26" t="n">
-        <v>0.104</v>
+        <v>0.04</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2096,200 +2094,198 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Kellogg's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Chocolate cereals, Mueslis, Mueslis with chocolate</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Flakes, Cereal flakes, Extruded cereals, Extruded flakes, Corn flakes</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1642</v>
+        <v>1604</v>
       </c>
       <c r="E27" t="n">
-        <v>9.6</v>
+        <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Muesli avoine chocolat bio</t>
+          <t>Corn Flakes</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.04</v>
+        <v>0.44</v>
       </c>
       <c r="M27" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>brioche pasquier</t>
+          <t>La Boulangère</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains grillés,Petits pains grillés,Pain grillé en tranches au froment</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Sliced breads,Multigrain sliced breads, Céréales et dérivés, en:Packaged breads</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1791</v>
+        <v>1306</v>
       </c>
       <c r="E28" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="F28" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pain de mie Bio grandes tranches céréales &amp; graines 500g</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Grilletine au froment sans sucres ajoutés</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Harrys</t>
+          <t>LU Pelletier</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pains de mie complet</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Rusks,Toasts</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1178</v>
+        <v>1636</v>
       </c>
       <c r="E29" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="F29" t="n">
-        <v>8.1</v>
+        <v>5.1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Pain de mie american sandwich complet sans sucres ajoutés 600g</t>
+          <t>Pain grillé au blé complet</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7.7</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
@@ -2299,125 +2295,123 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Harrys</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Frozen foods,Breads,Sliced breads,White breads,Bread white from wheat flour of the highest grade GOST 26987-86,Frozen breads,Multigrain sliced breads</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Breakfast cereals rich in fibre,Cereals with nuts,Crunchy cereal clusters,Cereal clusters with nuts</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1206</v>
+        <v>1949</v>
       </c>
       <c r="E30" t="n">
-        <v>6.5</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Harrys beau &amp; bon pain de mie farine de ble cereales &amp; graines 320g</t>
+          <t>Country Crisp 4 noix</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4</v>
+        <v>0.012</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>-7</v>
+        <v>9</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Quaker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals rich in fibre,Crunchy cereal clusters,Cereal clusters with chocolate</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1902</v>
+        <v>1570</v>
       </c>
       <c r="E31" t="n">
-        <v>16.7</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Country Crisp - Chocolat noir 70% cacao</t>
+          <t>Flocons d'avoine complète</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="L31" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="M31" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>D'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -2427,62 +2421,60 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nestlé, Chocapic</t>
+          <t>Maïzena, Unilever</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales extrudées,Céréales pour petit déjeuner riches en fibres,Pétales de blé chocolatés,Céréales pour petit déjeuner enrichies en vitamines et minéraux</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Aides culinaires, Amidons, Amidons de céréales, Amidon de maïs</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1648</v>
+        <v>1487</v>
       </c>
       <c r="E32" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NESTLE CHOCAPIC BIO Céréales 375g</t>
+          <t>Maizena Fleur de Maïs Sans Gluten 400g</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="K32" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08</v>
+        <v>0.004</v>
       </c>
       <c r="M32" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -2492,47 +2484,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lustucru,Lustucru selection</t>
+          <t>Tesco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Gnocchi,Gnocchi de semoule de blé dur,Gnocchi de pommes de terre,Gnocchis cuits</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales extrudées,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>801</v>
+        <v>1520</v>
       </c>
       <c r="E33" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Gnocchi à poêler</t>
+          <t>Malt Wheats</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="L33" t="n">
-        <v>0.44</v>
+        <v>0.107</v>
       </c>
       <c r="M33" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
@@ -2551,118 +2543,122 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Surgelés,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits,Pépites de céréales croustillantes,Pépites de céréales aux fruits,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Chocolate cereals, Mueslis, Mueslis with chocolate</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1818</v>
+        <v>1642</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Country Crisp 4 Baies</t>
+          <t>Muesli avoine chocolat bio</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="L34" t="n">
-        <v>0.012</v>
+        <v>0.04</v>
       </c>
       <c r="M34" t="n">
-        <v>20</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>brioche pasquier</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains grillés,Petits pains grillés,Pain grillé en tranches au froment</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nestlé,Chocapic</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals fortified with vitamins and chemical elements,Extruded cereals,Breakfast cereals rich in fibre,Chocolate wheat shells,Unfilled breakfast chocolate cereals fortified with vitamins and chemical elements</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1638</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>7</v>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Céréales Chocapic</t>
+          <t>Grilletine au froment sans sucres ajoutés</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.356</v>
       </c>
       <c r="M35" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -2681,51 +2677,51 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KRISPROLLS</t>
+          <t>Harrys</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Toasts,Toasted bread rolls</t>
+          <t>Pains de mie complet</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1680</v>
+        <v>1178</v>
       </c>
       <c r="E36" t="n">
-        <v>6.92</v>
+        <v>6.8</v>
       </c>
       <c r="F36" t="n">
-        <v>8.460000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Krisprolls complets sans sucres ajoutés</t>
+          <t>Pain de mie american sandwich complet sans sucres ajoutés 600g</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>13.1</v>
+        <v>7.7</v>
       </c>
       <c r="K36" t="n">
-        <v>0.769</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.431</v>
+        <v>0.44</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2740,53 +2736,55 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quaker</t>
+          <t>Nestlé, Chocapic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alimentos y bebidas de origen vegetal,Alimentos de origen vegetal,Desayunos,Cereales y patatas,Cereales y derivados,Cereales para el desayuno,Cereales de chocolate,en:Breakfast cereals rich in fibre,en:Crunchy cereal clusters,en:Cereal clusters with chocolate</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales extrudées,Céréales pour petit déjeuner riches en fibres,Pétales de blé chocolatés,Céréales pour petit déjeuner enrichies en vitamines et minéraux</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1906</v>
+        <v>1648</v>
       </c>
       <c r="E37" t="n">
-        <v>19</v>
+        <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cruesli Chocolat noir</t>
+          <t>NESTLE CHOCAPIC BIO Céréales 375g</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="K37" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="L37" t="n">
-        <v>0.192</v>
+        <v>0.08</v>
       </c>
       <c r="M37" t="n">
-        <v>16</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
       <c r="O37" t="n">
         <v>2</v>
       </c>
@@ -2797,32 +2795,32 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brownfield, CROWNFIELD</t>
+          <t>Warburtons</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alimente și băuturi pe bază de plante,Alimente pe bază de plante,en:Breakfasts,Cereale și cartofi,en:Cereals and their products,en:Breakfast cereals,en:Flakes,en:Cereal flakes,en:Extruded flakes,en:Rolled flakes,en:Rolled oats,Cereale</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Sliced breads,Wholemeal breads</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1556</v>
+        <v>953</v>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>2.23</v>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>6.47</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2830,24 +2828,24 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Haferflocken</t>
+          <t>Wholemeal Bread</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="K38" t="n">
-        <v>1.3</v>
+        <v>0.446</v>
       </c>
       <c r="L38" t="n">
-        <v>0.012</v>
+        <v>0.377</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7</v>
+        <v>2.46</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -2860,61 +2858,61 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Heudebert</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Rusks,Toasts,Multigrain rusks,Wholemeal rusks</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1618</v>
+        <v>1460</v>
       </c>
       <c r="E39" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>9.74</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Heudebert Fibre +</t>
+          <t>weetabix</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="K39" t="n">
-        <v>2.2</v>
+        <v>0.513</v>
       </c>
       <c r="L39" t="n">
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="M39" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2923,7 +2921,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -2933,51 +2931,51 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pågen</t>
+          <t>Oatly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Toasts,Toasted bread rolls</t>
+          <t>Rostlinné potraviny a nápoje,Nápoje,Rostlinné potraviny,Obiloviny a brambory,en:Dairy substitutes,Obiloviny,Náhražky mléka,en:Plant-based beverages,en:Plant-based milk alternatives,en:Cereal-based drinks,en:Unsweetened beverages,en:Oat-based drinks</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1687</v>
+        <v>166</v>
       </c>
       <c r="E40" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>7.7</v>
+        <v>0.8</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Krisprolls complets</t>
+          <t>Organic oat drink</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>1.1</v>
       </c>
       <c r="K40" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.64</v>
+        <v>0.0001</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2986,32 +2984,32 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Nestlé,Chocapic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Boissons,Aliments d'origine végétale,Céréales et pommes de terre,Substituts de produits laitiers,Céréales et dérivés,Substituts du lait,Boissons à base de végétaux,Boissons végétales,Boissons végétales de céréales,Boissons sans sucre ajouté,Boissons à l'avoine,Boissons-vegetales-a-base-d-avoine</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals fortified with vitamins and chemical elements,Extruded cereals,Breakfast cereals rich in fibre,Chocolate wheat shells,Unfilled breakfast chocolate cereals fortified with vitamins and chemical elements</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>187</v>
+        <v>1638</v>
       </c>
       <c r="E41" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3019,93 +3017,93 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Avoine - Boisson biologique</t>
+          <t>Céréales Chocapic</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.036</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>22.4</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Harrys</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Frozen foods,Breads,Sliced breads,White breads,Bread white from wheat flour of the highest grade GOST 26987-86,Frozen breads,Multigrain sliced breads</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>1</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nestlé, Chocapic</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales pour petit déjeuner enrichies en vitamines et minéraux,Céréales extrudées,Pétales de blé chocolatés,Céréales chocolatées pour petit déjeuner non fourrées mais enrichies en vitamines et minéraux,Céréales pour petit déjeuner riches en fibres</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1624</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F42" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NESTLE CHOCAPIC Céréales 375g</t>
+          <t>Harrys beau &amp; bon pain de mie farine de ble cereales &amp; graines 320g</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L42" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="M42" t="n">
-        <v>19.9</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3114,57 +3112,57 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Muesli Croustillant, Quaker</t>
+          <t>KRISPROLLS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Mueslis, Céréales aux fruits à coques, Mueslis aux fruits à coque</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Toasts,Toasted bread rolls</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1757</v>
+        <v>1680</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>6.92</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Muesli Croustillant Noix de pécan &amp; noix du Brésil</t>
+          <t>Krisprolls complets sans sucres ajoutés</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="K43" t="n">
-        <v>1.8</v>
+        <v>0.769</v>
       </c>
       <c r="L43" t="n">
-        <v>0.096</v>
+        <v>0.431</v>
       </c>
       <c r="M43" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
@@ -3177,133 +3175,131 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harry's</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains de mie</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Breakfast cereals rich in fibre,Crunchy cereal clusters,Cereal clusters with chocolate</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1233</v>
+        <v>1902</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>16.7</v>
       </c>
       <c r="F44" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Pain de mie american sandwich rustique sans sucres ajoutés 500g</t>
+          <t>Country Crisp - Chocolat noir 70% cacao</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4</v>
+        <v>0.012</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>20.8</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>-7</v>
+        <v>12</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quaker Oats</t>
+          <t>Indomie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Produits déshydratés,Pâtes alimentaires,Produits lyophilisés à reconstituer,Nouilles,Nouilles-instantes,Nouilles asiatiques aromatisées déshydratées</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1570</v>
+        <v>1870</v>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>15.7</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>4.29</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>-4</v>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Flocons d'avoine complète</t>
+          <t>Indomie Shrimp Noodles</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>8.57</v>
       </c>
       <c r="K45" t="n">
-        <v>1.5</v>
+        <v>7.14</v>
       </c>
       <c r="L45" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3353,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3372,89 +3368,89 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>La Boulangère Bio,La boulangere</t>
+          <t>Lustucru,Lustucru selection</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Tartine</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Gnocchi,Gnocchi de semoule de blé dur,Gnocchi de pommes de terre,Gnocchis cuits</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1318</v>
+        <v>801</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="F47" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tartines Bio quinoa &amp; graines 450g</t>
+          <t>Gnocchi à poêler</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Quaker</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
+          <t>Alimentos y bebidas de origen vegetal,Alimentos de origen vegetal,Desayunos,Cereales y patatas,Cereales y derivados,Cereales para el desayuno,Cereales de chocolate,en:Breakfast cereals rich in fibre,en:Crunchy cereal clusters,en:Cereal clusters with chocolate</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1569</v>
+        <v>1906</v>
       </c>
       <c r="E48" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="F48" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3462,32 +3458,32 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Muesli bio 36% fruits, noix &amp; graines</t>
+          <t>Cruesli Chocolat noir</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K48" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="L48" t="n">
-        <v>0.012</v>
+        <v>0.192</v>
       </c>
       <c r="M48" t="n">
-        <v>18.9</v>
+        <v>16</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3502,51 +3498,53 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Nestlé, Chocapic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Mueslis,Mueslis with chocolate</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales pour petit déjeuner enrichies en vitamines et minéraux,Céréales extrudées,Pétales de blé chocolatés,Céréales chocolatées pour petit déjeuner non fourrées mais enrichies en vitamines et minéraux,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1765</v>
+        <v>1624</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="F49" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Granola Chocolat</t>
+          <t>NESTLE CHOCAPIC Céréales 375g</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="K49" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.004</v>
+        <v>0.08</v>
       </c>
       <c r="M49" t="n">
-        <v>12</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -3555,70 +3553,70 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Crownfield,Bio Organic,Lidl</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Mueslis,Mueslis with chocolate,Crunchy cereal clusters,Cereal clusters with chocolate</t>
+          <t>Pflanzliche Lebensmittel und Getränke, Pflanzliche Lebensmittel, Frühstücke, Getreide und Kartoffeln, Getreideprodukte, Frühstückscerealien, Getreideflocken, Frühstücksflocken, Gerollte Flocken, Haferflocken</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1747</v>
+        <v>1561</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>6.7</v>
       </c>
       <c r="F50" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Crousti' Avoine Chocolat</t>
+          <t>Hafer Flocken Zart</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="K50" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>14</v>
+        <v>0.8</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -3628,53 +3626,51 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Heudebert</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales multicéréales,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Rusks,Toasts,Multigrain rusks,Wholemeal rusks</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1560</v>
+        <v>1618</v>
       </c>
       <c r="E51" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="F51" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Fitness Nature Céréales complètes</t>
+          <t>Heudebert Fibre +</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="L51" t="n">
-        <v>0.224</v>
+        <v>0.44</v>
       </c>
       <c r="M51" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -3689,116 +3685,114 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pasquier</t>
+          <t>Crownfield</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains grillés,Petits pains grillés</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Corn-flakes,Corn flakes natures</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1690</v>
+        <v>1615</v>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="F52" t="n">
-        <v>12.7</v>
+        <v>1.9</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Grilletine Sans sucres ajoutés Blé complet</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="L52" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="M52" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cookie crisp,Nestlé</t>
+          <t>Nestlé, Nestlé UK Ltd</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alimentos e bebidas à base de plantas,Alimentos à base de plantas,Pequenos alomoços,Cereais e Batatas,Cereais e seus produtos,Cereias para pequeno-almoçco,Cereais de chocolate,en:Extruded cereals</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales extrudées,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1659</v>
+        <v>1522</v>
       </c>
       <c r="E53" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>12.2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+        <v>-6</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>original shredded wheat</t>
+        </is>
+      </c>
       <c r="J53" t="n">
-        <v>6.7</v>
+        <v>12.2</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L53" t="n">
-        <v>0.264</v>
+        <v>0.02</v>
       </c>
       <c r="M53" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -3807,70 +3801,70 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KELLOG'S</t>
+          <t>Pågen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Extruded cereals, Honey cereal balls, en:cereals-with-honey</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Breads,Toasts,Toasted bread rolls</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1607</v>
+        <v>1687</v>
       </c>
       <c r="E54" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="F54" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Miel pops</t>
+          <t>Krisprolls complets</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="M54" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -3880,85 +3874,85 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains complets,Pain complet 3 céréales,Pain complet</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Surgelés,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits,Pépites de céréales croustillantes,Pépites de céréales aux fruits,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>824</v>
+        <v>1818</v>
       </c>
       <c r="E55" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Pain complet 3 céréales</t>
+          <t>Country Crisp 4 Baies</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="L55" t="n">
-        <v>0.44</v>
+        <v>0.012</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Mueslis, Mueslis au chocolat</t>
+          <t>Aliments et boissons à base de végétaux,Boissons,Aliments d'origine végétale,Céréales et pommes de terre,Substituts de produits laitiers,Céréales et dérivés,Substituts du lait,Boissons à base de végétaux,Boissons végétales,Boissons végétales de céréales,Boissons sans sucre ajouté,Boissons à l'avoine,Boissons-vegetales-a-base-d-avoine</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1672</v>
+        <v>187</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="F56" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3966,37 +3960,37 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Muesli bio chocolat noir</t>
+          <t>Avoine - Boisson biologique</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="K56" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="M56" t="n">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -4006,51 +4000,53 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BRIOCHE PASQUIER</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains grillés,B</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales multicéréales,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1643</v>
+        <v>1560</v>
       </c>
       <c r="E57" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="n">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pain Grillé l'Original</t>
+          <t>Fitness Nature Céréales complètes</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L57" t="n">
-        <v>0.52</v>
+        <v>0.224</v>
       </c>
       <c r="M57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
       <c r="O57" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -4069,51 +4065,51 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Tesco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Galettes de céréales soufflées, Galettes de riz soufflé, Galettes de riz complet soufflé</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales de blé,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1580</v>
+        <v>1485</v>
       </c>
       <c r="E58" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="F58" t="n">
-        <v>3.6</v>
+        <v>15.7</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Galettes riz complet Bio</t>
+          <t>Bran Flakes Malty Crunch</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="K58" t="n">
-        <v>0.699</v>
+        <v>0.5</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1</v>
+        <v>0.236</v>
       </c>
       <c r="M58" t="n">
-        <v>0.599</v>
+        <v>10.2</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -4128,64 +4124,64 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HERTA, Tarte en or</t>
+          <t>yum yum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pâtes à tarte,Pâtes feuilletées,Pâte feuilletée à la matière grasse végétale, Aides culinaires, en:Baking Mixes, en:Frozen baking mixes, en:Refrigerated baking mixes</t>
+          <t>Pflanzliche Lebensmittel und Getränke,Pflanzliche Lebensmittel,Getreide und Kartoffeln,Fertiggerichte,Getreideprodukte,Getrocknete Produkte,Teigwaren,Suppen,Getrocknete Produkte zur Rehydrierung,Nudeln,Getrocknete Fertiggerichte,Instant-Nudeln,Instantsuppen,Instant Nudelsuppen</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1601.8</v>
+        <v>263</v>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>3.54</v>
       </c>
       <c r="F59" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HERTA TARTE EN OR Pâte Feuilletée 230g</t>
+          <t>Chicken Flavour</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>6.5</v>
+        <v>0.98</v>
       </c>
       <c r="K59" t="n">
-        <v>9.199999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="L59" t="n">
-        <v>0.48</v>
+        <v>0.252</v>
       </c>
       <c r="M59" t="n">
-        <v>1.9</v>
+        <v>0.27</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -4195,51 +4191,51 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lustucru, Lustucru selection</t>
+          <t>Kellogg's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Surgelés, Gnocchi, Gnocchi de pommes de terre, Céréales et dérivés, Gnocchi de semoule de blé dur</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales de blé,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>801</v>
+        <v>1509</v>
       </c>
       <c r="E60" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="F60" t="n">
-        <v>2.6</v>
+        <v>17</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Lustucru gnocchi a poêler format xxl 720g</t>
+          <t>Bran Flakes</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L60" t="n">
-        <v>0.44</v>
+        <v>0.264</v>
       </c>
       <c r="M60" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -4258,22 +4254,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gerblé</t>
+          <t>Crownfield</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germe de blé</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales multicéréales,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1572</v>
+        <v>1620</v>
       </c>
       <c r="E61" t="n">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="F61" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4281,28 +4277,28 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Germe de blé</t>
+          <t>Special Flakes Classic</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K61" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="L61" t="n">
-        <v>0.008</v>
+        <v>0.204</v>
       </c>
       <c r="M61" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -4311,65 +4307,65 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Muesli Croustillant, Quaker</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Mueslis, Céréales aux fruits à coques, Mueslis aux fruits à coque</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1757</v>
+      </c>
+      <c r="E62" t="n">
+        <v>11</v>
+      </c>
+      <c r="F62" t="n">
+        <v>13</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>1</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Kellogg's</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Extruded cereals, Honey cereal balls, en:cereals-with-honey</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1607</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>9</v>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Céréales Miel Pops</t>
+          <t>Muesli Croustillant Noix de pécan &amp; noix du Brésil</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="L62" t="n">
-        <v>0.16</v>
+        <v>0.096</v>
       </c>
       <c r="M62" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4384,51 +4380,51 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Crownfield,Lidl</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales aux fruits, Mueslis, Mueslis aux fruits</t>
+          <t>Alimentos y bebidas de origen vegetal,Alimentos de origen vegetal,Desayunos,Cereales y patatas,Cereales y derivados,Cereales para el desayuno,Copos,Copos de cereales,en:Extruded cereals,en:Extruded flakes,en:Breakfast cereals rich in fibre,en:Extruded wheat flakes</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="E63" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>9.4</v>
+        <v>17.2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Muesli Bio Superfruits</t>
+          <t>Bran Flakes</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0.012</v>
+        <v>0.252</v>
       </c>
       <c r="M63" t="n">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -4437,7 +4433,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -4447,22 +4443,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Flocons, Flocons de céréales, Flocons laminés, Flocons d'avoine</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1524</v>
+        <v>1566</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4474,24 +4470,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Flocons d'avoine</t>
+          <t>Oat flakes</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>10.8333333333333</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -4506,64 +4502,64 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Quaker Oats</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Breakfast cereals rich in fibre, Cereals with nuts, Crunchy cereal clusters, Cereal clusters with nuts, en:mueslis</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1847</v>
+        <v>1570</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Croustillant 3 noix</t>
+          <t>Flocons d'avoine complète</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="L65" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="M65" t="n">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -4573,22 +4569,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Harry's</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Puffed cereal cakes,Puffed corn cakes</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains de mie</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1594</v>
+        <v>1233</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4596,28 +4592,28 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Galette de mais</t>
+          <t>Pain de mie american sandwich rustique sans sucres ajoutés 500g</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L66" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -4636,22 +4632,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alpro</t>
+          <t>KELLOG'S</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Beverages and beverages preparations, Plant-based foods and beverages, Beverages, Plant-based foods, Cereals and potatoes, Dairy substitutes, Cereals and their products, Milk substitutes, Plant-based beverages, Plant-based milk alternatives, Cereal-based drinks, Unsweetened beverages, Oat-based drinks</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Extruded cereals, Honey cereal balls, en:cereals-with-honey</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>188</v>
+        <v>1607</v>
       </c>
       <c r="E67" t="n">
         <v>1.5</v>
       </c>
       <c r="F67" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4659,32 +4655,32 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Oat</t>
+          <t>Miel pops</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L67" t="n">
-        <v>8</v>
+        <v>0.16</v>
       </c>
       <c r="M67" t="n">
-        <v>3.2</v>
+        <v>22</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -4695,181 +4691,181 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Pépites de céréales croustillantes, Pépites de céréales au chocolat, en:Aliments d'origine végétale, en:Aliments et boissons à base de végétaux, en:Céréales au chocolat, en:Céréales et dérivés, en:Céréales et pommes de terre, en:Céréales pour petit-déjeuner, en:Petit-déjeuners, en:Pépites de céréales au chocolat, en:Pépites de céréales croustillantes</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2076</v>
+        <v>1531</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>22</v>
+        <v>-3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Céréales Extra Pépites Chocolat Noisettes</t>
+          <t>Weetabix</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>0.6</v>
       </c>
       <c r="L68" t="n">
-        <v>0.272</v>
+        <v>0.112</v>
       </c>
       <c r="M68" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>11</v>
+        <v>-4</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>D'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quaker</t>
+          <t>Kellogg's</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Pépites de céréales croustillantes,Pépites de céréales au chocolat,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales extrudées,Céréales pour petit déjeuner riches en fibres,Bâtonnets de son de blé,Céréales pour petit déjeuner à base de son de blé</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1914</v>
+        <v>1400</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>3.5</v>
       </c>
       <c r="F69" t="n">
-        <v>8.699999999999999</v>
+        <v>27</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Quaker Cruesli Chocolat au lait</t>
+          <t>Céréales All Bran Kellogg's Fibre Plus</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>7.7</v>
+        <v>14</v>
       </c>
       <c r="K69" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="L69" t="n">
-        <v>0.204</v>
+        <v>0.38</v>
       </c>
       <c r="M69" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>D'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>La Boulangère Bio,La boulangere</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Bircher-style mueslis,Mueslis with fruits,Bircher-style mueslis with fruits</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Tartine</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1498</v>
+        <v>1318</v>
       </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Muesli aux fruits</t>
+          <t>Tartines Bio quinoa &amp; graines 450g</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="K70" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="L70" t="n">
-        <v>0.008</v>
+        <v>0.4</v>
       </c>
       <c r="M70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -4878,67 +4874,65 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nestlé, Chocapic</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales pour petit déjeuner enrichies en vitamines et minéraux,Céréales extrudées,Pétales de blé chocolatés,Céréales chocolatées pour petit déjeuner non fourrées mais enrichies en vitamines et minéraux,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Cereals with fruits,Mueslis,Mueslis with fruits</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1624</v>
+        <v>1569</v>
       </c>
       <c r="E71" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="F71" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>chocapic</t>
+          <t>Muesli bio 36% fruits, noix &amp; graines</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="L71" t="n">
-        <v>0.08</v>
+        <v>0.012</v>
       </c>
       <c r="M71" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -4953,87 +4947,85 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Vemondo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pâte feuilletée pur beurre,Pate-a-derouler</t>
+          <t>Boissons et préparations de boissons, Aliments et boissons à base de végétaux, Boissons, Aliments d'origine végétale, Céréales et pommes de terre, Substituts de produits laitiers, Céréales et dérivés, Substituts du lait, Boissons à base de végétaux, Boissons végétales, Boissons végétales de céréales, Boissons à l'avoine, en:A</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1557</v>
+        <v>148</v>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>1.2</v>
       </c>
       <c r="F72" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Pâte à tarte feuilletée - Pur beurre</t>
+          <t>Bio Hafer</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>15</v>
+        <v>0.2</v>
       </c>
       <c r="L72" t="n">
-        <v>0.48</v>
+        <v>0.032</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+        <v>3.3</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales au chocolat,Céréales pour petit déjeuner enrichies en vitamines et minéraux,Céréales extrudées,Pétales de blé chocolatés,Céréales chocolatées pour petit déjeuner non fourrées mais enrichies en vitamines et minéraux,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Breakfast cereals rich in fibre,Granola</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1638</v>
+        <v>1741</v>
       </c>
       <c r="E73" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5041,37 +5033,37 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>NESTLE CHOCAPIC Céréales 750g</t>
+          <t>Crunchy Oat Granola Raisin &amp; Almond</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="M73" t="n">
-        <v>22.4</v>
+        <v>21</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -5081,51 +5073,51 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vemondo</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boissons et préparations de boissons, Aliments et boissons à base de végétaux, Boissons, Aliments d'origine végétale, Céréales et pommes de terre, Substituts de produits laitiers, Céréales et dérivés, Substituts du lait, Boissons à base de végétaux, Boissons végétales, Boissons végétales de céréales, Boissons à l'avoine, en:A</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Rices,Aromatic rices,Indica rices,Long grain rices,Brown rices,Basmati rices,Brown Basmati rices</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>148</v>
+        <v>545</v>
       </c>
       <c r="E74" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Bio Hafer</t>
+          <t>Tilda Steamed Brown Basmati Rice</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M74" t="n">
         <v>0.2</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="M74" t="n">
-        <v>3.3</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -5144,60 +5136,60 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lustucru, Lustucru selection</t>
+          <t>Kallø</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Gnocchi, Gnocchi de pommes de terre, Céréales et dérivés, Gnocchi de semoule de blé dur</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Galettes de céréales soufflées,Galettes de riz soufflé,en:Rice cake</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>801</v>
+        <v>2039</v>
       </c>
       <c r="E75" t="n">
-        <v>2.7</v>
+        <v>24.1</v>
       </c>
       <c r="F75" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Lustucru gnocchi a poêler 520g</t>
+          <t>Belgian Dark Chocolate Rice Cake Thins imp</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3</v>
+        <v>14.6</v>
       </c>
       <c r="L75" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>1.5</v>
+        <v>23.4</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
-        <v>-3</v>
+        <v>18</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
@@ -5207,186 +5199,186 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>Lidl</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Beverages and beverages preparations, Plant-based foods and beverages, Beverages, Plant-based foods, Dairy substitutes, Milk substitutes, Nuts and their products, Plant-based beverages, Plant-based milk alternatives, Nut-based drinks, Hazelnut-based drinks, Sweetened beverages, en:cereal-based-drinks</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Aliments à base de fruits et de légumes,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Fruits et produits dérivés,Céréales pour petit-déjeuner,Fruits,Céréales aux fruits,Mueslis,Mueslis aux fruits</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>286</v>
+        <v>1650</v>
       </c>
       <c r="E76" t="n">
-        <v>4.5</v>
+        <v>11.6</v>
       </c>
       <c r="F76" t="n">
-        <v>1.1</v>
+        <v>6.44</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Boisson Noisette</t>
+          <t>Premium Fruit &amp; Nut Muesli</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>0.4</v>
+        <v>4.67</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02</v>
+        <v>0.0178</v>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>24.7</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tipiak</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Plats préparés,Assortiments d'aliments,Assortiments de céréales - grains et légumes secs,céréales et dérivés</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Mueslis,Mueslis with chocolate,Crunchy cereal clusters,Cereal clusters with chocolate</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>616</v>
+        <v>1747</v>
       </c>
       <c r="E77" t="n">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="F77" t="n">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Céréales Méditerranéennes</t>
+          <t>Crousti' Avoine Chocolat</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="L77" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Taureau Ailé</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Graines,Céréales et dérivés,Céréales en grains,Riz,Riz parfumés,Riz de variété indica,Riz long grain,Riz Basmati,Riz Basmati blancs</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Breakfasts,Cereals and potatoes,Cereals and their products,Breakfast cereals,Chocolate cereals,Mueslis,Mueslis with chocolate</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1497</v>
+        <v>1765</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8</v>
+        <v>13</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Riz basmati du Penjab</t>
+          <t>Granola Chocolat</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="L78" t="n">
         <v>0.004</v>
       </c>
       <c r="M78" t="n">
-        <v>0.2</v>
+        <v>12</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
@@ -5396,51 +5388,51 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>bjorg</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Galettes de céréales soufflées, Galettes de riz soufflé, Galettes de riz complet soufflé</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1598</v>
+        <v>1580</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="F79" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Muesli Protéines</t>
+          <t>Galettes riz complet Bio</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>21</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>1.9</v>
+        <v>0.699</v>
       </c>
       <c r="L79" t="n">
-        <v>0.012</v>
+        <v>0.1</v>
       </c>
       <c r="M79" t="n">
-        <v>11</v>
+        <v>0.599</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -5449,7 +5441,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -5459,22 +5451,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Barilla</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
+          <t>Pflanzliche Lebensmittel und Getränke,Pflanzliche Lebensmittel,Getreide und Kartoffeln,Getreideprodukte,Teigwaren,en:Cereal pastas,Getrocknete Teigwaren,Hartweizenteigwaren,Spaghettis,en:Whole durum wheat pasta,en:Dry durum wheat pasta,Hartweizenspaghetti,Vollkorn-Hartweizenspaghetti,Vollkorn Hartweizen</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1566</v>
+        <v>1466</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5486,20 +5478,20 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Oat flakes</t>
+          <t>Pâtes spaghetti au blé complet integral 500g</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K80" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
@@ -5512,7 +5504,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -5522,22 +5514,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tipiak</t>
+          <t>CROWNFIELD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Graines,Quinoa</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Flakes, Cereal flakes, Rolled flakes, Rolled oats, en:extruded-flakes</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1515</v>
+        <v>1566</v>
       </c>
       <c r="E81" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5545,28 +5537,28 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Quinoa Gourmand</t>
+          <t>Fiocchi di avena integrali</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="M81" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -5581,217 +5573,215 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Pasquier</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Extruded cereals, Filled cereals, en:chocolate-cereals</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains grillés,Petits pains grillés</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1838</v>
+        <v>1690</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>3.7</v>
+        <v>12.7</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tresor - Choco Nut</t>
+          <t>Grilletine Sans sucres ajoutés Blé complet</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="K82" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="L82" t="n">
-        <v>0.376</v>
+        <v>0.36</v>
       </c>
       <c r="M82" t="n">
-        <v>26</v>
+        <v>2.1</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Warburtons</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,White breads,Sliced breads</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Farmhouse Soft Bread</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Nestlé, Lion</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Céréales extrudées, Céréales au caramel</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1709</v>
-      </c>
-      <c r="E83" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F83" t="n">
-        <v>7</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>11</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>NESTLE LION céréales 400g​</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="M83" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>6</v>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bien</t>
+          <t>Tesco</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains de mie,en:Packaged breads,Pains complets,Pains de mie complet</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Flakes, Cereal flakes, Extruded cereals, Extruded flakes, Corn flakes</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1060</v>
+        <v>1619</v>
       </c>
       <c r="E84" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="F84" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>PAIN MIE SANDWICH BIO* COMPLET Sans sucres ajoutés 500G</t>
+          <t>Corn Flakes</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L84" t="n">
-        <v>0.396</v>
+        <v>0.236</v>
       </c>
       <c r="M84" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Rude health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Rusks,Wholemeal rusks</t>
+          <t>Dranken en drankbereidingen,Plantaardige levensmiddelen en dranken,Dranken,Plantaardige levensmiddelen,Granen en aardappels,Zuivelvervangers,Granen en graanproducten,Melkvervangers,Plantaardige dranken,Plantaardige melken,Tarwemelken,Haverdranken</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1637</v>
+        <v>205</v>
       </c>
       <c r="E85" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="F85" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5803,28 +5793,28 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Biscottes Complètes bio</t>
+          <t>Organic Oat Drink imp</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="L85" t="n">
-        <v>0.52</v>
+        <v>0.036</v>
       </c>
       <c r="M85" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -5835,55 +5825,55 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brioche Pasquier,Pasquier</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Toasts,Crispbreads,Toasted bread rolls</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales pour petit déjeuner riches en fibres</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1787</v>
+        <v>1516</v>
       </c>
       <c r="E86" t="n">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="F86" t="n">
-        <v>6.3</v>
+        <v>12</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Grilletine froment</t>
+          <t>Grape-Nuts</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="L86" t="n">
-        <v>0.352</v>
+        <v>0.4</v>
       </c>
       <c r="M86" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -5892,61 +5882,61 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marque Repère, Grainéa</t>
+          <t>ALPRO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Flocons laminés,Flocons d'avoine</t>
+          <t>Plant-based foods and beverages, Dairy substitutes, Getreide und Kartoffeln, Getreidemilch, Getreideprodukte, Getränke, Getränke und Getränkezubereitungen, Hafermilch, Milchersatz, Pflanzenmilch, Pflanzliche Getränke, Pflanzliche Lebensmittel, Pflanzliche Lebensmittel und Getränke, en:oat-based-drinks</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1556</v>
+        <v>248</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Flocons d'avoine</t>
+          <t>Alpro Not Milk</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>14</v>
+        <v>0.7</v>
       </c>
       <c r="K87" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="L87" t="n">
-        <v>0.01</v>
+        <v>0.048</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -5955,70 +5945,70 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jordans</t>
+          <t>Kellogg's</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Mueslis,Céréales pour petit déjeuner riches en fibres</t>
+          <t>Plant-based foods and beverages, Plant-based foods, Breakfasts, Cereals and potatoes, Cereals and their products, Breakfast cereals, Extruded cereals, Honey cereal balls, en:cereals-with-honey</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1892</v>
+        <v>1607</v>
       </c>
       <c r="E88" t="n">
-        <v>14.8</v>
+        <v>1.5</v>
       </c>
       <c r="F88" t="n">
-        <v>16.1</v>
+        <v>4.6</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Granola Amandes Noisettes &amp; Graines</t>
+          <t>Céréales Miel Pops</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>12.6</v>
+        <v>5.2</v>
       </c>
       <c r="K88" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="L88" t="n">
-        <v>0.012</v>
+        <v>0.16</v>
       </c>
       <c r="M88" t="n">
-        <v>2.5</v>
+        <v>22</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
@@ -6028,51 +6018,51 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ebly</t>
+          <t>Gerblé</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Graines,Céréales et dérivés,Céréales en grains,Semoules de céréales,Semoules de blé,Semoules de blé dur,Blés,Blés durs,Blé dur précuit entier</t>
+          <t>Germe de blé</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>565</v>
+        <v>1572</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5</v>
+        <v>9.6</v>
       </c>
       <c r="F89" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>L'original</t>
+          <t>Germe de blé</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="L89" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -6081,191 +6071,191 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>A'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Crownfield,Bio Organic,Lidl</t>
+          <t>leader food</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pflanzliche Lebensmittel und Getränke, Pflanzliche Lebensmittel, Frühstücke, Getreide und Kartoffeln, Getreideprodukte, Frühstückscerealien, Getreideflocken, Frühstücksflocken, Gerollte Flocken, Haferflocken</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Snacks, Céréales et pommes de terre, Snacks salés, Graines, Amuse-gueules, Céréales et dérivés, Chips et frites, Céréales en grains, Chips, Chips de pommes de terre, Maïs, Chips de pommes de terre aromatisées, Chips barbecue</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1561</v>
+        <v>2145</v>
       </c>
       <c r="E90" t="n">
-        <v>6.7</v>
+        <v>25</v>
       </c>
       <c r="F90" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Hafer Flocken Zart</t>
+          <t>Fakiat Barbeque</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="K90" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="M90" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>B'</t>
+          <t>C'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Marque Repère, Grainéa</t>
+          <t>Jordans</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Mueslis, Mueslis croustillants, Mueslis au chocolat, Mueslis croustillant au chocolat, Muesli croustillant au chocolat non enrichi en vitamines et minéraux</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Mueslis, Mueslis au chocolat</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1810</v>
+        <v>1672</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Muesli pépites croustillantes chocolat-noissette réduit en sucre</t>
+          <t>Muesli bio chocolat noir</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="K91" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="L91" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="M91" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>B'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tarte en or, Herta</t>
+          <t>Aldi,Acti Leaf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Aides culinaires,Pâtes à tarte,Pâtes brisées,Pâte brisée cuite à la matière grasse végétale, Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Aides culinaires, Pâtes à tarte, en:Baking Mixes, Pâtes brisées, en:Frozen baking mixes, en:Refrigerated baking mixes</t>
+          <t>Beverages and beverages preparations,Plant-based foods and beverages,Beverages,Plant-based foods,Cereals and potatoes,Dairy substitutes,Cereals and their products,Milk substitutes,Plant-based beverages,Plant-based milk alternatives,Cereal-based drinks,Oat-based drinks</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1622</v>
+        <v>205</v>
       </c>
       <c r="E92" t="n">
-        <v>20</v>
+        <v>2.4</v>
       </c>
       <c r="F92" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>HERTA TARTE EN OR Pâte Brisée 230g</t>
+          <t>Oat</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="K92" t="n">
-        <v>9.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L92" t="n">
-        <v>0.4</v>
+        <v>0.015</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -6276,26 +6266,26 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Unilever</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plant-based foods and beverages, Plant-based foods, Cereals and potatoes, Cereals and their products, Starches, Cereal starches, Corn starch, fr:Fleur de maïs en poudre, en:cooking-helpers</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E93" t="n">
         <v>1</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Maitre Jean Pierre</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Breads,Sliced breads</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1190</v>
-      </c>
-      <c r="E93" t="n">
-        <v>4.4</v>
-      </c>
       <c r="F93" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6303,32 +6293,28 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Pain de mie extra-moelleux nature</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.36</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -6343,22 +6329,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tipiak</t>
+          <t>Lustucru, Lustucru selection</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Céréales et dérivés, Plats préparés, Semoules de céréales, Semoules de blé, Semoules de blé dur, Couscous, Semoules de blé dur pour couscous</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Céréales et pommes de terre, Surgelés, Gnocchi, Gnocchi de pommes de terre, Céréales et dérivés, Gnocchi de semoule de blé dur</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="E94" t="n">
-        <v>1.29</v>
+        <v>2.7</v>
       </c>
       <c r="F94" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6366,32 +6352,32 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tipiak Graine Parfumé</t>
+          <t>Lustucru gnocchi a poêler format xxl 720g</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>5.86</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>0.214</v>
+        <v>0.3</v>
       </c>
       <c r="L94" t="n">
-        <v>0.267</v>
+        <v>0.44</v>
       </c>
       <c r="M94" t="n">
         <v>1.5</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -6406,26 +6392,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brets</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Snacks,Céréales et pommes de terre,Snacks salés,Graines,Amuse-gueules,Céréales et dérivés,Chips et frites,Céréales en grains,Chips,Sarrasin,en:Chips-de-sarrasin</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Pains,Pains complets,Pain complet 3 céréales,Pain complet</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2359</v>
+        <v>824</v>
       </c>
       <c r="E95" t="n">
-        <v>38</v>
+        <v>2.9</v>
       </c>
       <c r="F95" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -6433,96 +6419,96 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Chips de Sarrasin au Sel de Guerande</t>
+          <t>Pain complet 3 céréales</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>8.9</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="L95" t="n">
         <v>0.44</v>
       </c>
       <c r="M95" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Céréales au chocolat, Pépites de céréales croustillantes, Pépites de céréales au chocolat</t>
+          <t>Plant-based foods and beverages,Plant-based foods,Cereals and potatoes,Cereals and their products,Puffed cereal cakes,Puffed corn cakes</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2026</v>
+        <v>1594</v>
       </c>
       <c r="E96" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Céréales Extra Kellogg's Pépites Chocolat au lait</t>
+          <t>Galette de mais</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K96" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="L96" t="n">
-        <v>0.272</v>
+        <v>0.12</v>
       </c>
       <c r="M96" t="n">
-        <v>25</v>
+        <v>0.8</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>D'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
@@ -6532,51 +6518,51 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Bjorg</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Céréales extrudées,Céréales pour petit déjeuner riches en fibres,Bâtonnets de son de blé,Céréales pour petit déjeuner à base de son de blé</t>
+          <t>Aliments et boissons à base de végétaux, Aliments d'origine végétale, Petit-déjeuners, Céréales et pommes de terre, Céréales et dérivés, Céréales pour petit-déjeuner, Flocons, Flocons de céréales, Flocons laminés, Flocons d'avoine</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1400</v>
+        <v>1524</v>
       </c>
       <c r="E97" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Céréales All Bran Kellogg's Fibre Plus</t>
+          <t>Flocons d'avoine</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>14</v>
+        <v>10.8333333333333</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0.38</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="M97" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -6585,67 +6571,65 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>C'</t>
+          <t>A'</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Barilla</t>
+          <t>BRIOCHE PASQUIER</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cibi e bevande a base vegetale, Cibi a base vegetale, Cereali e patate, Cereali e i loro prodotti, Pasta, Paste alimentari di cereali, Pasta secca, Pasta di grano duro, Paste all'uovo, Pasta al'uovo secca, en:Lasagna sheets, fr:Lasagnes à garnir aux œufs</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pains,Pains grillés,B</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1558</v>
+        <v>1643</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Lasagne all'uovo</t>
+          <t>Pain Grillé l'Original</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K98" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M98" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="L98" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="M98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>-4</v>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -6660,184 +6644,58 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bjorg</t>
+          <t>HERTA, Tarte en or</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Aliments d'origine végétale,Céréales pour petit-déjeuner,Céréales aux fruits,Mueslis,Mueslis aux fruits</t>
+          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Céréales et pommes de terre,Céréales et dérivés,Pâtes à tarte,Pâtes feuilletées,Pâte feuilletée à la matière grasse végétale, Aides culinaires, en:Baking Mixes, en:Frozen baking mixes, en:Refrigerated baking mixes</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1485</v>
+        <v>1601.8</v>
       </c>
       <c r="E99" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Muesli</t>
+          <t>HERTA TARTE EN OR Pâte Feuilletée 230g</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="K99" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L99" t="n">
-        <v>0.012</v>
+        <v>0.48</v>
       </c>
       <c r="M99" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
-        <v>-3</v>
+        <v>15</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
-        <is>
-          <t>C'</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>0</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Kellogg's</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Aliments et boissons à base de végétaux,Aliments d'origine végétale,Petit-déjeuners,Céréales et pommes de terre,Céréales et dérivés,Céréales pour petit-déjeuner,Flocons,Flocons de céréales,Céréales extrudées,Flocons extrudés,Pétales multicéréales,Céréales pour petit déjeuner riches en fibres</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1640</v>
-      </c>
-      <c r="E100" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F100" t="n">
-        <v>6</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>9</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Cereales special K original</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>8</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="M100" t="n">
-        <v>15</v>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>C'</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>0</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Barilla</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Pflanzliche Lebensmittel und Getränke,Pflanzliche Lebensmittel,Getreide und Kartoffeln,Getreideprodukte,Teigwaren,en:Cereal pastas,Getrocknete Teigwaren,Hartweizenteigwaren,Spaghettis,en:Whole durum wheat pasta,en:Dry durum wheat pasta,Hartweizenspaghetti,Vollkorn-Hartweizenspaghetti,Vollkorn Hartweizen</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1466</v>
-      </c>
-      <c r="E101" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F101" t="n">
-        <v>8</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Pâtes spaghetti au blé complet integral 500g</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>13</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="M101" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
         <is>
           <t>A'</t>
         </is>

--- a/outputs/excel/dataset_avec_preds.xlsx
+++ b/outputs/excel/dataset_avec_preds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,31 @@
           <t>electre_cat</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>is_bio</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>green_points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>electre_points</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>super_score</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>super_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +638,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -697,6 +739,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -781,6 +840,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -865,6 +941,23 @@
           <t>B'</t>
         </is>
       </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,6 +1042,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1033,6 +1143,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1117,6 +1244,23 @@
           <t>B'</t>
         </is>
       </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1201,6 +1345,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1285,6 +1446,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1369,6 +1547,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1453,6 +1648,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1537,6 +1749,23 @@
           <t>B'</t>
         </is>
       </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1621,6 +1850,23 @@
           <t>B'</t>
         </is>
       </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1705,6 +1951,23 @@
           <t>B'</t>
         </is>
       </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1789,6 +2052,23 @@
           <t>A'</t>
         </is>
       </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1873,6 +2153,23 @@
           <t>D'</t>
         </is>
       </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1957,6 +2254,23 @@
           <t>D'</t>
         </is>
       </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2041,6 +2355,23 @@
           <t>D'</t>
         </is>
       </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2125,6 +2456,23 @@
           <t>D'</t>
         </is>
       </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2209,6 +2557,23 @@
           <t>D'</t>
         </is>
       </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2293,6 +2658,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2377,6 +2759,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2461,6 +2860,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2545,6 +2961,23 @@
           <t>C'</t>
         </is>
       </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2627,6 +3060,23 @@
       <c r="T26" t="inlineStr">
         <is>
           <t>C'</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
